--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -400,8 +400,11 @@
     <t>InFulfillmentOf.order</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Order
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Order {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-order}
 </t>
+  </si>
+  <si>
+    <t>Prescription</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1284,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1382,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1485,7 +1488,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1893,7 +1896,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2004,7 +2007,9 @@
       <c r="K13" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>​InFulfillmentOf permet d'Associer un document à une prescription .</t>
+    <t>​InFulfillmentOf permet d'Associer un document à une prescription.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="129">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>InFulfillmentOf.typeId.nullFlavor</t>
@@ -1260,7 +1264,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1268,10 +1272,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1369,17 +1373,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1397,11 +1401,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1452,7 +1456,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1472,17 +1476,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1500,11 +1504,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1555,7 +1559,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1575,17 +1579,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1603,11 +1607,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1616,7 +1620,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1658,7 +1662,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1678,17 +1682,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1706,11 +1710,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1761,7 +1765,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1781,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1811,7 +1815,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1862,7 +1866,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1882,10 +1886,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1919,7 +1923,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -1941,7 +1945,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1959,7 +1963,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -1979,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2005,10 +2009,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2060,7 +2064,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>​InFulfillmentOf permet d'Associer un document à une prescription.</t>
+    <t>L'élément de l'en-tête du CDA inFulfillmentOf permet d'associer un document à une prescription.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-inFulfillment-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
